--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/expected-participant</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/expected-participant</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T13:18:28+00:00</t>
+    <t>2026-10-29T07:06:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
     <t>affiliation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/affiliation}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/affiliation}
 </t>
   </si>
   <si>
@@ -466,7 +466,7 @@
     <t>primaryTrack</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/primary-track}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/primary-track}
 </t>
   </si>
   <si>
@@ -659,7 +659,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/identifier/participant-2026</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/identifier/participant-2026</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1289,7 +1289,7 @@
     <t>Person.link.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/checked-in-participant)
+    <t xml:space="preserve">Reference(https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/checked-in-participant)
 </t>
   </si>
   <si>
@@ -1632,7 +1632,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.98046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.96484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:06:30+00:00</t>
+    <t>2026-10-29T08:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:26:45+00:00</t>
+    <t>2026-10-29T09:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:23:29+00:00</t>
+    <t>2026-10-29T13:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:05:39+00:00</t>
+    <t>2026-10-29T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:50:41+00:00</t>
+    <t>2026-10-29T16:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-expected-participant.xlsx
+++ b/StructureDefinition-expected-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T16:44:10+00:00</t>
+    <t>2026-10-30T09:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
